--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.71467402446339</v>
+        <v>1.091134528975301</v>
       </c>
       <c r="D2" t="n">
-        <v>6.953940213265077</v>
+        <v>1.130015284655575</v>
       </c>
       <c r="E2" t="n">
-        <v>15.18036745831339</v>
+        <v>2.466809711975926</v>
       </c>
       <c r="F2" t="n">
-        <v>15.08014319496397</v>
+        <v>2.450523269181645</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.07463604568851</v>
+        <v>2.287128357424383</v>
       </c>
       <c r="D3" t="n">
-        <v>17.55730169339204</v>
+        <v>2.853061525176207</v>
       </c>
       <c r="E3" t="n">
-        <v>15.18036745831339</v>
+        <v>2.466809711975926</v>
       </c>
       <c r="F3" t="n">
-        <v>15.08014319496397</v>
+        <v>2.450523269181645</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.783562133944004</v>
+        <v>1.427328846765901</v>
       </c>
       <c r="D4" t="n">
-        <v>9.135447999608092</v>
+        <v>1.484510299936315</v>
       </c>
       <c r="E4" t="n">
-        <v>15.18036745831339</v>
+        <v>2.466809711975926</v>
       </c>
       <c r="F4" t="n">
-        <v>15.08014319496397</v>
+        <v>2.450523269181645</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.65399373778129</v>
+        <v>4.81877398238946</v>
       </c>
       <c r="D5" t="n">
-        <v>32.59425156027108</v>
+        <v>5.296565878544051</v>
       </c>
       <c r="E5" t="n">
-        <v>15.18036745831339</v>
+        <v>2.466809711975926</v>
       </c>
       <c r="F5" t="n">
-        <v>15.08014319496397</v>
+        <v>2.450523269181645</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.69340568928649</v>
+        <v>2.712678424509054</v>
       </c>
       <c r="D6" t="n">
-        <v>27.41801288327072</v>
+        <v>4.455427093531491</v>
       </c>
       <c r="E6" t="n">
-        <v>15.18036745831339</v>
+        <v>2.466809711975926</v>
       </c>
       <c r="F6" t="n">
-        <v>15.08014319496397</v>
+        <v>2.450523269181645</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.50661627748738</v>
+        <v>8.0448251450917</v>
       </c>
       <c r="D7" t="n">
-        <v>51.35382548884397</v>
+        <v>8.344996641937145</v>
       </c>
       <c r="E7" t="n">
-        <v>15.18036745831339</v>
+        <v>2.466809711975926</v>
       </c>
       <c r="F7" t="n">
-        <v>15.08014319496397</v>
+        <v>2.450523269181645</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.79341462357009</v>
+        <v>6.466429876330141</v>
       </c>
       <c r="D8" t="n">
-        <v>39.64281657664409</v>
+        <v>6.441957693704665</v>
       </c>
       <c r="E8" t="n">
-        <v>15.18036745831339</v>
+        <v>2.466809711975926</v>
       </c>
       <c r="F8" t="n">
-        <v>15.08014319496397</v>
+        <v>2.450523269181645</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
